--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/149.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/149.xlsx
@@ -426,13 +426,13 @@
         <v>-9.347327391295165</v>
       </c>
       <c r="E2">
-        <v>-3.963204787896499</v>
+        <v>-5.462351579661764</v>
       </c>
       <c r="F2">
-        <v>-4.620965479952069</v>
+        <v>-4.723577745478179</v>
       </c>
       <c r="G2">
-        <v>-5.074455011446299</v>
+        <v>-6.850373992169552</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.68427357317584</v>
       </c>
       <c r="E3">
-        <v>-5.147432440220352</v>
+        <v>-6.405542145979346</v>
       </c>
       <c r="F3">
-        <v>-5.04079087292887</v>
+        <v>-4.654184503381369</v>
       </c>
       <c r="G3">
-        <v>-4.754451058529267</v>
+        <v>-6.455386182788028</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-8.048336658887415</v>
       </c>
       <c r="E4">
-        <v>-4.576310355320981</v>
+        <v>-6.684473502481802</v>
       </c>
       <c r="F4">
-        <v>-5.125687804084875</v>
+        <v>-4.926253301859501</v>
       </c>
       <c r="G4">
-        <v>-3.738643265259296</v>
+        <v>-5.991952844382072</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.513932959873583</v>
       </c>
       <c r="E5">
-        <v>-4.784828469478171</v>
+        <v>-6.610120487749862</v>
       </c>
       <c r="F5">
-        <v>-4.829165794419401</v>
+        <v>-4.5238811399238</v>
       </c>
       <c r="G5">
-        <v>-3.003741882087564</v>
+        <v>-5.65936881841581</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.063935644209374</v>
       </c>
       <c r="E6">
-        <v>-5.961588668163374</v>
+        <v>-8.242309317386473</v>
       </c>
       <c r="F6">
-        <v>-5.053770134758854</v>
+        <v>-4.023533803382396</v>
       </c>
       <c r="G6">
-        <v>-4.101267181448905</v>
+        <v>-6.732124616052324</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-6.703666434976092</v>
       </c>
       <c r="E7">
-        <v>-7.249984808085668</v>
+        <v>-8.28045265395308</v>
       </c>
       <c r="F7">
-        <v>-5.148656290976493</v>
+        <v>-4.376328051635265</v>
       </c>
       <c r="G7">
-        <v>-3.544142093736035</v>
+        <v>-6.213911680608049</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.400296151172864</v>
       </c>
       <c r="E8">
-        <v>-7.596458354412527</v>
+        <v>-9.245293854501334</v>
       </c>
       <c r="F8">
-        <v>-4.987800072998266</v>
+        <v>-4.45758879400942</v>
       </c>
       <c r="G8">
-        <v>-3.860948059662131</v>
+        <v>-6.238230948139535</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.144938122277547</v>
       </c>
       <c r="E9">
-        <v>-7.27449290941518</v>
+        <v>-10.65586369467657</v>
       </c>
       <c r="F9">
-        <v>-5.006576490331716</v>
+        <v>-4.322737027162709</v>
       </c>
       <c r="G9">
-        <v>-3.681814440532167</v>
+        <v>-5.952431551734253</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.902644249846661</v>
       </c>
       <c r="E10">
-        <v>-8.246366830097346</v>
+        <v>-11.12587854040668</v>
       </c>
       <c r="F10">
-        <v>-5.071003230677708</v>
+        <v>-4.245516318578839</v>
       </c>
       <c r="G10">
-        <v>-4.231318652413634</v>
+        <v>-4.689342559408421</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.654510904381169</v>
       </c>
       <c r="E11">
-        <v>-9.514153884810732</v>
+        <v>-11.22759259509296</v>
       </c>
       <c r="F11">
-        <v>-4.873902319118734</v>
+        <v>-4.409076714407679</v>
       </c>
       <c r="G11">
-        <v>-3.437608738282288</v>
+        <v>-5.765614156407641</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.383609418990759</v>
       </c>
       <c r="E12">
-        <v>-10.04482763987359</v>
+        <v>-13.34623463110753</v>
       </c>
       <c r="F12">
-        <v>-5.219383805307062</v>
+        <v>-4.411561548989003</v>
       </c>
       <c r="G12">
-        <v>-3.433520214541288</v>
+        <v>-5.822499260408938</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.072000450422117</v>
       </c>
       <c r="E13">
-        <v>-11.56691568096171</v>
+        <v>-13.20149101640037</v>
       </c>
       <c r="F13">
-        <v>-4.918283301840051</v>
+        <v>-4.395772001012072</v>
       </c>
       <c r="G13">
-        <v>-3.20485090250721</v>
+        <v>-5.404493227892861</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.726419287632548</v>
       </c>
       <c r="E14">
-        <v>-11.79871015151833</v>
+        <v>-14.06628464069716</v>
       </c>
       <c r="F14">
-        <v>-4.491215621711946</v>
+        <v>-3.888621855710898</v>
       </c>
       <c r="G14">
-        <v>-3.515979282833455</v>
+        <v>-3.979945619071234</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.345598612674385</v>
       </c>
       <c r="E15">
-        <v>-11.74224008064268</v>
+        <v>-13.84270029351645</v>
       </c>
       <c r="F15">
-        <v>-4.453715049340255</v>
+        <v>-3.860896708102258</v>
       </c>
       <c r="G15">
-        <v>-2.484919806264062</v>
+        <v>-4.137577244923631</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-3.946177726504856</v>
       </c>
       <c r="E16">
-        <v>-14.36253288180495</v>
+        <v>-15.35322714046299</v>
       </c>
       <c r="F16">
-        <v>-3.867203816910495</v>
+        <v>-3.267530404617518</v>
       </c>
       <c r="G16">
-        <v>-3.061914788303637</v>
+        <v>-4.360181637529765</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-3.547517453423146</v>
       </c>
       <c r="E17">
-        <v>-14.56992340593423</v>
+        <v>-15.90526170742003</v>
       </c>
       <c r="F17">
-        <v>-3.724135783774484</v>
+        <v>-3.302788449412946</v>
       </c>
       <c r="G17">
-        <v>-2.88856138168524</v>
+        <v>-4.378717382004145</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-3.165881122171459</v>
       </c>
       <c r="E18">
-        <v>-15.57088824364167</v>
+        <v>-17.3715272494156</v>
       </c>
       <c r="F18">
-        <v>-3.240292246577874</v>
+        <v>-2.978530998050381</v>
       </c>
       <c r="G18">
-        <v>-2.40548326604925</v>
+        <v>-3.817682540009395</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-2.831174597005236</v>
       </c>
       <c r="E19">
-        <v>-15.71208153472682</v>
+        <v>-17.77575242476228</v>
       </c>
       <c r="F19">
-        <v>-3.376806904635797</v>
+        <v>-3.226505294731016</v>
       </c>
       <c r="G19">
-        <v>-2.633487158429935</v>
+        <v>-4.170967407232721</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-2.557304215005408</v>
       </c>
       <c r="E20">
-        <v>-17.67527464348009</v>
+        <v>-19.97799009095844</v>
       </c>
       <c r="F20">
-        <v>-2.513805166811999</v>
+        <v>-2.391512187874722</v>
       </c>
       <c r="G20">
-        <v>-1.484145200287921</v>
+        <v>-3.429487970074456</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-2.365715748624057</v>
       </c>
       <c r="E21">
-        <v>-17.47651991928344</v>
+        <v>-19.52216295429436</v>
       </c>
       <c r="F21">
-        <v>-2.127163955734358</v>
+        <v>-2.410359080121409</v>
       </c>
       <c r="G21">
-        <v>-1.64640496880422</v>
+        <v>-3.935359191748329</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.266917142015519</v>
       </c>
       <c r="E22">
-        <v>-18.11716313714856</v>
+        <v>-19.51713181967184</v>
       </c>
       <c r="F22">
-        <v>-2.002999036405032</v>
+        <v>-1.907191955197565</v>
       </c>
       <c r="G22">
-        <v>-1.969222885429632</v>
+        <v>-3.079834771307712</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.26123135528476</v>
       </c>
       <c r="E23">
-        <v>-18.92976609850695</v>
+        <v>-20.7022515813752</v>
       </c>
       <c r="F23">
-        <v>-1.822219798010577</v>
+        <v>-1.280826763405771</v>
       </c>
       <c r="G23">
-        <v>-2.289465197625491</v>
+        <v>-3.844547617060581</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.352312340566554</v>
       </c>
       <c r="E24">
-        <v>-18.22920211257233</v>
+        <v>-20.13315372435726</v>
       </c>
       <c r="F24">
-        <v>-1.343901810752936</v>
+        <v>-1.777218794423365</v>
       </c>
       <c r="G24">
-        <v>-1.880440675157457</v>
+        <v>-3.210382824103332</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.522494852901008</v>
       </c>
       <c r="E25">
-        <v>-19.49300411015897</v>
+        <v>-20.31872606071758</v>
       </c>
       <c r="F25">
-        <v>-1.33926788724436</v>
+        <v>-1.188613902773394</v>
       </c>
       <c r="G25">
-        <v>-2.151964999197401</v>
+        <v>-3.699846982084577</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-2.761994761268499</v>
       </c>
       <c r="E26">
-        <v>-19.52500683597118</v>
+        <v>-20.39536142634939</v>
       </c>
       <c r="F26">
-        <v>-1.474487865716411</v>
+        <v>-1.480794974524648</v>
       </c>
       <c r="G26">
-        <v>-1.390691810259835</v>
+        <v>-3.789890510207214</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-3.050755953874081</v>
       </c>
       <c r="E27">
-        <v>-19.59101840158099</v>
+        <v>-20.80248935353498</v>
       </c>
       <c r="F27">
-        <v>-0.956385602157015</v>
+        <v>-1.151844210681678</v>
       </c>
       <c r="G27">
-        <v>-2.259792777957003</v>
+        <v>-4.343393861100121</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.367472406086981</v>
       </c>
       <c r="E28">
-        <v>-18.75637988570127</v>
+        <v>-21.15474123269563</v>
       </c>
       <c r="F28">
-        <v>-0.976653870462809</v>
+        <v>-0.8953313635579512</v>
       </c>
       <c r="G28">
-        <v>-2.519564665332535</v>
+        <v>-3.141738662346544</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-3.697511564772253</v>
       </c>
       <c r="E29">
-        <v>-19.31339124559274</v>
+        <v>-20.56461314238607</v>
       </c>
       <c r="F29">
-        <v>-1.134826498767324</v>
+        <v>-1.036721460276554</v>
       </c>
       <c r="G29">
-        <v>-2.915201341639756</v>
+        <v>-2.674534612571358</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-4.016517234415033</v>
       </c>
       <c r="E30">
-        <v>-18.42992672296232</v>
+        <v>-20.58881330748306</v>
       </c>
       <c r="F30">
-        <v>-0.9992200960519058</v>
+        <v>-1.214307155692526</v>
       </c>
       <c r="G30">
-        <v>-2.769159935720347</v>
+        <v>-4.367977972274748</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-4.311777435824871</v>
       </c>
       <c r="E31">
-        <v>-18.01998661341796</v>
+        <v>-20.18250956256686</v>
       </c>
       <c r="F31">
-        <v>-1.01115727938953</v>
+        <v>-1.045313856720771</v>
       </c>
       <c r="G31">
-        <v>-2.445021111424766</v>
+        <v>-3.953822104220845</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-4.56520862838179</v>
       </c>
       <c r="E32">
-        <v>-18.41694811645634</v>
+        <v>-19.29132399175336</v>
       </c>
       <c r="F32">
-        <v>-1.027532006702217</v>
+        <v>-0.9853032803199816</v>
       </c>
       <c r="G32">
-        <v>-3.147230857396195</v>
+        <v>-3.737726244144918</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.760097340755142</v>
       </c>
       <c r="E33">
-        <v>-17.46355036972547</v>
+        <v>-19.80816325872279</v>
       </c>
       <c r="F33">
-        <v>-1.313875538449161</v>
+        <v>-1.843408199453241</v>
       </c>
       <c r="G33">
-        <v>-2.586232431402378</v>
+        <v>-4.768282517792342</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.885494608971752</v>
       </c>
       <c r="E34">
-        <v>-17.48060913131236</v>
+        <v>-18.5178244034512</v>
       </c>
       <c r="F34">
-        <v>-1.432744545197258</v>
+        <v>-1.311080297508411</v>
       </c>
       <c r="G34">
-        <v>-2.790883735549044</v>
+        <v>-3.683211490749739</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.926679653463055</v>
       </c>
       <c r="E35">
-        <v>-16.44360216897788</v>
+        <v>-17.97869145894202</v>
       </c>
       <c r="F35">
-        <v>-1.761369857474605</v>
+        <v>-1.713949743101559</v>
       </c>
       <c r="G35">
-        <v>-2.436668605029184</v>
+        <v>-4.304912079751633</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.879984511060253</v>
       </c>
       <c r="E36">
-        <v>-15.95093589626139</v>
+        <v>-17.66344174089805</v>
       </c>
       <c r="F36">
-        <v>-1.631739569031098</v>
+        <v>-1.915088312891946</v>
       </c>
       <c r="G36">
-        <v>-2.14547632994043</v>
+        <v>-4.709665998474007</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.74237290761482</v>
       </c>
       <c r="E37">
-        <v>-15.05730042100975</v>
+        <v>-16.76246560927997</v>
       </c>
       <c r="F37">
-        <v>-2.023005201381821</v>
+        <v>-1.91893117529576</v>
       </c>
       <c r="G37">
-        <v>-2.511960342228829</v>
+        <v>-3.415606852628292</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.518722223104973</v>
       </c>
       <c r="E38">
-        <v>-15.59730283252841</v>
+        <v>-16.93981423684236</v>
       </c>
       <c r="F38">
-        <v>-1.757603012954732</v>
+        <v>-1.719653459956014</v>
       </c>
       <c r="G38">
-        <v>-2.654654786608035</v>
+        <v>-3.613458296237295</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.221039513046294</v>
       </c>
       <c r="E39">
-        <v>-13.82346333593187</v>
+        <v>-15.71658736636445</v>
       </c>
       <c r="F39">
-        <v>-1.959696557412129</v>
+        <v>-1.611031822333769</v>
       </c>
       <c r="G39">
-        <v>-2.279109811178651</v>
+        <v>-3.450086184419801</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.861131082470586</v>
       </c>
       <c r="E40">
-        <v>-14.52425827404088</v>
+        <v>-17.1537348204907</v>
       </c>
       <c r="F40">
-        <v>-2.41219221971853</v>
+        <v>-1.458374449879772</v>
       </c>
       <c r="G40">
-        <v>-1.907285888935407</v>
+        <v>-3.864414200841748</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.461310050343414</v>
       </c>
       <c r="E41">
-        <v>-13.57942387165851</v>
+        <v>-15.09289422671004</v>
       </c>
       <c r="F41">
-        <v>-2.362532745181053</v>
+        <v>-1.852254780696886</v>
       </c>
       <c r="G41">
-        <v>-2.082595827967513</v>
+        <v>-3.173745016620218</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.039636925045772</v>
       </c>
       <c r="E42">
-        <v>-13.29007249646441</v>
+        <v>-14.17980895559545</v>
       </c>
       <c r="F42">
-        <v>-2.109283124096089</v>
+        <v>-2.146954736706647</v>
       </c>
       <c r="G42">
-        <v>-1.665798144573271</v>
+        <v>-4.209637889676947</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.617838644290391</v>
       </c>
       <c r="E43">
-        <v>-12.29458711230625</v>
+        <v>-13.16756821760891</v>
       </c>
       <c r="F43">
-        <v>-2.084856835909309</v>
+        <v>-2.19642812579906</v>
       </c>
       <c r="G43">
-        <v>-1.678278901256323</v>
+        <v>-2.921852227628152</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.217268985151157</v>
       </c>
       <c r="E44">
-        <v>-12.25940992621466</v>
+        <v>-13.52448442499746</v>
       </c>
       <c r="F44">
-        <v>-2.155228016408903</v>
+        <v>-1.935704204646179</v>
       </c>
       <c r="G44">
-        <v>-1.585629973794279</v>
+        <v>-3.176082261770943</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.851371296496163</v>
       </c>
       <c r="E45">
-        <v>-11.95667238185388</v>
+        <v>-14.3864160537214</v>
       </c>
       <c r="F45">
-        <v>-2.331935546894763</v>
+        <v>-1.787472498372878</v>
       </c>
       <c r="G45">
-        <v>-1.367620618396654</v>
+        <v>-3.676285829481584</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.539107837920393</v>
       </c>
       <c r="E46">
-        <v>-10.44621799049147</v>
+        <v>-12.75485668197185</v>
       </c>
       <c r="F46">
-        <v>-2.208766778586249</v>
+        <v>-1.565305481437286</v>
       </c>
       <c r="G46">
-        <v>-1.141761959525416</v>
+        <v>-3.275448286132168</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.285826458443742</v>
       </c>
       <c r="E47">
-        <v>-10.24791611369558</v>
+        <v>-12.20942915859201</v>
       </c>
       <c r="F47">
-        <v>-2.526193706335524</v>
+        <v>-2.289929331193647</v>
       </c>
       <c r="G47">
-        <v>-1.035837744450896</v>
+        <v>-3.649791533530796</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.097026805860869</v>
       </c>
       <c r="E48">
-        <v>-10.3441009016185</v>
+        <v>-11.5892229439235</v>
       </c>
       <c r="F48">
-        <v>-2.485277872157188</v>
+        <v>-2.69367931727578</v>
       </c>
       <c r="G48">
-        <v>-0.9180915712556373</v>
+        <v>-3.384302334008944</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.9725959090412023</v>
       </c>
       <c r="E49">
-        <v>-9.978177559428698</v>
+        <v>-11.10161497667358</v>
       </c>
       <c r="F49">
-        <v>-2.352154720317178</v>
+        <v>-2.139356907577326</v>
       </c>
       <c r="G49">
-        <v>-0.6999067569444305</v>
+        <v>-3.799987674101991</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.9044804895854742</v>
       </c>
       <c r="E50">
-        <v>-9.913343397060881</v>
+        <v>-10.71205752863775</v>
       </c>
       <c r="F50">
-        <v>-2.484988053974662</v>
+        <v>-2.12019723341234</v>
       </c>
       <c r="G50">
-        <v>-1.110814979824309</v>
+        <v>-3.645120353774885</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.890102229791618</v>
       </c>
       <c r="E51">
-        <v>-8.686471105006797</v>
+        <v>-11.22882886849706</v>
       </c>
       <c r="F51">
-        <v>-2.532481810672776</v>
+        <v>-2.122708199141269</v>
       </c>
       <c r="G51">
-        <v>-1.132833418206002</v>
+        <v>-4.079318264523537</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.9166801753959644</v>
       </c>
       <c r="E52">
-        <v>-8.742669467441987</v>
+        <v>-11.01369012534066</v>
       </c>
       <c r="F52">
-        <v>-2.444812602311794</v>
+        <v>-1.718989095324488</v>
       </c>
       <c r="G52">
-        <v>-0.7902416130745233</v>
+        <v>-3.742096164256756</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-0.9767394417348182</v>
       </c>
       <c r="E53">
-        <v>-7.89971214481018</v>
+        <v>-10.34944450094755</v>
       </c>
       <c r="F53">
-        <v>-2.717423820065964</v>
+        <v>-1.871249749446667</v>
       </c>
       <c r="G53">
-        <v>-1.143466890478141</v>
+        <v>-3.599143497325487</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-1.061509326926157</v>
       </c>
       <c r="E54">
-        <v>-6.739462762356943</v>
+        <v>-9.188683400931447</v>
       </c>
       <c r="F54">
-        <v>-2.649664962473887</v>
+        <v>-2.240276191479832</v>
       </c>
       <c r="G54">
-        <v>-1.131764111996818</v>
+        <v>-3.239307060479944</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-1.162628023567122</v>
       </c>
       <c r="E55">
-        <v>-6.885266039981905</v>
+        <v>-9.368278151601647</v>
       </c>
       <c r="F55">
-        <v>-2.55950775211975</v>
+        <v>-1.99029692311025</v>
       </c>
       <c r="G55">
-        <v>-1.262838541533182</v>
+        <v>-3.705186892039421</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-1.279079942480821</v>
       </c>
       <c r="E56">
-        <v>-6.080370541384568</v>
+        <v>-7.736121021283088</v>
       </c>
       <c r="F56">
-        <v>-2.484909660531848</v>
+        <v>-2.475390796127099</v>
       </c>
       <c r="G56">
-        <v>-1.657862766915638</v>
+        <v>-4.028087572303315</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-1.404797492432101</v>
       </c>
       <c r="E57">
-        <v>-5.926352611909691</v>
+        <v>-7.793917935042985</v>
       </c>
       <c r="F57">
-        <v>-2.703734266132905</v>
+        <v>-2.199921781048519</v>
       </c>
       <c r="G57">
-        <v>-2.161741040174869</v>
+        <v>-4.236615525276468</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-1.540185929208402</v>
       </c>
       <c r="E58">
-        <v>-6.324577559196207</v>
+        <v>-8.026740369199342</v>
       </c>
       <c r="F58">
-        <v>-2.67710108375296</v>
+        <v>-2.269904161745873</v>
       </c>
       <c r="G58">
-        <v>-1.619000272830133</v>
+        <v>-4.398603829058547</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-1.683186928013181</v>
       </c>
       <c r="E59">
-        <v>-5.341998325959908</v>
+        <v>-7.94914496707791</v>
       </c>
       <c r="F59">
-        <v>-2.77169187881737</v>
+        <v>-2.758768838547383</v>
       </c>
       <c r="G59">
-        <v>-2.025396222139985</v>
+        <v>-3.909202571442548</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-1.831092725525077</v>
       </c>
       <c r="E60">
-        <v>-4.527457177726234</v>
+        <v>-8.036789053022362</v>
       </c>
       <c r="F60">
-        <v>-2.930463147957921</v>
+        <v>-2.438278231704691</v>
       </c>
       <c r="G60">
-        <v>-2.94543655404992</v>
+        <v>-3.660878550541816</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-1.98337320847015</v>
       </c>
       <c r="E61">
-        <v>-4.936233469450621</v>
+        <v>-7.004804168362379</v>
       </c>
       <c r="F61">
-        <v>-3.27066535047713</v>
+        <v>-2.554560254839917</v>
       </c>
       <c r="G61">
-        <v>-1.878911203118314</v>
+        <v>-3.669207883118622</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-2.133135217849554</v>
       </c>
       <c r="E62">
-        <v>-5.266472436459982</v>
+        <v>-6.823253116920867</v>
       </c>
       <c r="F62">
-        <v>-2.720825620372328</v>
+        <v>-2.895011891040808</v>
       </c>
       <c r="G62">
-        <v>-2.045176731737131</v>
+        <v>-5.651009690929151</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-2.277164351292754</v>
       </c>
       <c r="E63">
-        <v>-5.595361918215057</v>
+        <v>-7.048594512016551</v>
       </c>
       <c r="F63">
-        <v>-2.815535193380395</v>
+        <v>-2.43070495001706</v>
       </c>
       <c r="G63">
-        <v>-2.46094483546866</v>
+        <v>-4.624515456658412</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-2.408642824858931</v>
       </c>
       <c r="E64">
-        <v>-4.34441172986219</v>
+        <v>-6.656510175484437</v>
       </c>
       <c r="F64">
-        <v>-2.932961444039526</v>
+        <v>-3.019361312109283</v>
       </c>
       <c r="G64">
-        <v>-2.979207429096025</v>
+        <v>-5.363336525748641</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.521074334239046</v>
       </c>
       <c r="E65">
-        <v>-4.352929789470618</v>
+        <v>-6.817307230548796</v>
       </c>
       <c r="F65">
-        <v>-3.000789984691882</v>
+        <v>-2.521722904536238</v>
       </c>
       <c r="G65">
-        <v>-2.451758071597182</v>
+        <v>-4.397885440676524</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.609519207182281</v>
       </c>
       <c r="E66">
-        <v>-4.370441398458279</v>
+        <v>-6.156693442309844</v>
       </c>
       <c r="F66">
-        <v>-2.853084068782507</v>
+        <v>-3.142473067004842</v>
       </c>
       <c r="G66">
-        <v>-2.483982921876448</v>
+        <v>-4.571891024766157</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.665491643269517</v>
       </c>
       <c r="E67">
-        <v>-4.075058095885957</v>
+        <v>-5.542093478462831</v>
       </c>
       <c r="F67">
-        <v>-2.991256075080937</v>
+        <v>-2.914238080854243</v>
       </c>
       <c r="G67">
-        <v>-2.839836772438247</v>
+        <v>-5.070601536438587</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.684952174065824</v>
       </c>
       <c r="E68">
-        <v>-4.308922079064078</v>
+        <v>-5.814639686614472</v>
       </c>
       <c r="F68">
-        <v>-3.312314440494314</v>
+        <v>-3.680227537268925</v>
       </c>
       <c r="G68">
-        <v>-2.648010521710717</v>
+        <v>-5.006158456971134</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.662115294152738</v>
       </c>
       <c r="E69">
-        <v>-4.117344986169583</v>
+        <v>-6.441040853725474</v>
       </c>
       <c r="F69">
-        <v>-3.229787525240765</v>
+        <v>-3.379408141601906</v>
       </c>
       <c r="G69">
-        <v>-2.279036979176787</v>
+        <v>-4.592128389647722</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.593441097500232</v>
       </c>
       <c r="E70">
-        <v>-4.635719405827609</v>
+        <v>-5.907550387829844</v>
       </c>
       <c r="F70">
-        <v>-3.513389662048084</v>
+        <v>-3.391552790414454</v>
       </c>
       <c r="G70">
-        <v>-2.14039133199211</v>
+        <v>-4.479761852953779</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-2.477940134943678</v>
       </c>
       <c r="E71">
-        <v>-4.590914683995718</v>
+        <v>-5.882670951631703</v>
       </c>
       <c r="F71">
-        <v>-3.538636309899061</v>
+        <v>-3.403307847571803</v>
       </c>
       <c r="G71">
-        <v>-1.949594660927293</v>
+        <v>-4.249662385246736</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-2.314664199325378</v>
       </c>
       <c r="E72">
-        <v>-4.892397841056372</v>
+        <v>-6.95033568299812</v>
       </c>
       <c r="F72">
-        <v>-3.567721069036107</v>
+        <v>-3.012907710503867</v>
       </c>
       <c r="G72">
-        <v>-1.772794976402515</v>
+        <v>-4.587960412813779</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-2.108715711785417</v>
       </c>
       <c r="E73">
-        <v>-4.576473380385258</v>
+        <v>-7.392504942055069</v>
       </c>
       <c r="F73">
-        <v>-3.668567502466503</v>
+        <v>-3.687976610313171</v>
       </c>
       <c r="G73">
-        <v>-1.465136047801426</v>
+        <v>-4.166120768563228</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-1.865100272069369</v>
       </c>
       <c r="E74">
-        <v>-5.194940661034821</v>
+        <v>-6.555339537679074</v>
       </c>
       <c r="F74">
-        <v>-3.380296600620468</v>
+        <v>-3.753561831536307</v>
       </c>
       <c r="G74">
-        <v>-1.864785105302244</v>
+        <v>-3.673379170498104</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-1.591917672710612</v>
       </c>
       <c r="E75">
-        <v>-5.589103567136457</v>
+        <v>-7.772484667564681</v>
       </c>
       <c r="F75">
-        <v>-3.87939439319459</v>
+        <v>-3.401339301118912</v>
       </c>
       <c r="G75">
-        <v>-0.7212663967638082</v>
+        <v>-4.196829388985507</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-1.299358282197458</v>
       </c>
       <c r="E76">
-        <v>-6.485895388771448</v>
+        <v>-7.238998730143059</v>
       </c>
       <c r="F76">
-        <v>-3.653526255534616</v>
+        <v>-3.656557468656767</v>
       </c>
       <c r="G76">
-        <v>-1.121421967732134</v>
+        <v>-3.61720583378775</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-0.9971252585354673</v>
       </c>
       <c r="E77">
-        <v>-6.65014766950366</v>
+        <v>-7.883500207862721</v>
       </c>
       <c r="F77">
-        <v>-4.015364256417602</v>
+        <v>-3.670170212852927</v>
       </c>
       <c r="G77">
-        <v>-1.673534889498547</v>
+        <v>-3.388976824310395</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-0.6991722235996058</v>
       </c>
       <c r="E78">
-        <v>-6.661849246339481</v>
+        <v>-8.233542191707624</v>
       </c>
       <c r="F78">
-        <v>-3.835162278829324</v>
+        <v>-3.846044714027266</v>
       </c>
       <c r="G78">
-        <v>0.03344529091492289</v>
+        <v>-2.760327400221571</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-0.4165354943175925</v>
       </c>
       <c r="E79">
-        <v>-6.600538236749631</v>
+        <v>-10.27407710803789</v>
       </c>
       <c r="F79">
-        <v>-4.002148230553259</v>
+        <v>-3.089603420576769</v>
       </c>
       <c r="G79">
-        <v>-0.9281125926030112</v>
+        <v>-2.459329289245495</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-0.1615999013311971</v>
       </c>
       <c r="E80">
-        <v>-7.244867632457001</v>
+        <v>-9.606503055249153</v>
       </c>
       <c r="F80">
-        <v>-3.729038145435727</v>
+        <v>-4.077360008183394</v>
       </c>
       <c r="G80">
-        <v>-0.6959539655705407</v>
+        <v>-2.167147161040499</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>0.05505615063587379</v>
       </c>
       <c r="E81">
-        <v>-9.096080635948596</v>
+        <v>-10.63027781653323</v>
       </c>
       <c r="F81">
-        <v>-4.352513073931844</v>
+        <v>-3.809561672706245</v>
       </c>
       <c r="G81">
-        <v>0.094362639383052</v>
+        <v>-2.567276247644511</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>0.2263845641231997</v>
       </c>
       <c r="E82">
-        <v>-10.6086543531466</v>
+        <v>-11.44703791703066</v>
       </c>
       <c r="F82">
-        <v>-4.589460818176232</v>
+        <v>-4.114662617315656</v>
       </c>
       <c r="G82">
-        <v>-0.0121707160706948</v>
+        <v>-2.272581415375208</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>0.3421980263357423</v>
       </c>
       <c r="E83">
-        <v>-11.00638116829228</v>
+        <v>-11.2690598315812</v>
       </c>
       <c r="F83">
-        <v>-4.339588449955943</v>
+        <v>-4.169940288588154</v>
       </c>
       <c r="G83">
-        <v>0.2892577658254861</v>
+        <v>-2.597862377881837</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>0.3994517831149614</v>
       </c>
       <c r="E84">
-        <v>-12.51702575556302</v>
+        <v>-12.657526190125</v>
       </c>
       <c r="F84">
-        <v>-4.736116737063671</v>
+        <v>-4.54145631632039</v>
       </c>
       <c r="G84">
-        <v>0.3412995417028291</v>
+        <v>-1.506607251771876</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>0.3926010738763218</v>
       </c>
       <c r="E85">
-        <v>-13.26529268669443</v>
+        <v>-13.9145807614402</v>
       </c>
       <c r="F85">
-        <v>-4.599963163954469</v>
+        <v>-4.389156861403282</v>
       </c>
       <c r="G85">
-        <v>-0.02953452742417217</v>
+        <v>-2.19348917189648</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>0.3188406685187927</v>
       </c>
       <c r="E86">
-        <v>-13.85429318697609</v>
+        <v>-15.98173404798756</v>
       </c>
       <c r="F86">
-        <v>-4.750621107690224</v>
+        <v>-4.603467905145337</v>
       </c>
       <c r="G86">
-        <v>0.287486623961976</v>
+        <v>-0.5473468868581963</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>0.1789820954416467</v>
       </c>
       <c r="E87">
-        <v>-15.63052824632268</v>
+        <v>-16.1249877947462</v>
       </c>
       <c r="F87">
-        <v>-4.773245138545234</v>
+        <v>-4.421496136196556</v>
       </c>
       <c r="G87">
-        <v>1.112510988349288</v>
+        <v>-1.499886844327156</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.0312162181960502</v>
       </c>
       <c r="E88">
-        <v>-17.25854182292422</v>
+        <v>-18.04127949820203</v>
       </c>
       <c r="F88">
-        <v>-5.017803381566266</v>
+        <v>-4.29188247666516</v>
       </c>
       <c r="G88">
-        <v>1.096805760310985</v>
+        <v>-0.1650682618019346</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.306949859071306</v>
       </c>
       <c r="E89">
-        <v>-18.45894971287748</v>
+        <v>-20.66036772527826</v>
       </c>
       <c r="F89">
-        <v>-4.856910738351984</v>
+        <v>-4.559584206081468</v>
       </c>
       <c r="G89">
-        <v>0.4635182619216428</v>
+        <v>-0.7924431258581387</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.6493788752127947</v>
       </c>
       <c r="E90">
-        <v>-19.49114290734182</v>
+        <v>-21.50427602745167</v>
       </c>
       <c r="F90">
-        <v>-5.253060519745923</v>
+        <v>-4.507933221355325</v>
       </c>
       <c r="G90">
-        <v>0.3399256653040316</v>
+        <v>-0.9150392482684293</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.054252793137707</v>
       </c>
       <c r="E91">
-        <v>-20.37655467379553</v>
+        <v>-22.7839548549092</v>
       </c>
       <c r="F91">
-        <v>-4.899362767268297</v>
+        <v>-4.909364661977254</v>
       </c>
       <c r="G91">
-        <v>0.1232305964854968</v>
+        <v>-1.41964915209184</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.513759701951534</v>
       </c>
       <c r="E92">
-        <v>-23.05761053919272</v>
+        <v>-24.39653992056661</v>
       </c>
       <c r="F92">
-        <v>-5.211130321928748</v>
+        <v>-5.041283405468572</v>
       </c>
       <c r="G92">
-        <v>-0.2182885918912582</v>
+        <v>-1.062275761127515</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.023425145227022</v>
       </c>
       <c r="E93">
-        <v>-25.20626730093013</v>
+        <v>-26.21081869005165</v>
       </c>
       <c r="F93">
-        <v>-5.158646307891085</v>
+        <v>-4.550781968603455</v>
       </c>
       <c r="G93">
-        <v>-0.3430663638119285</v>
+        <v>-0.7611319861477118</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.566918590869871</v>
       </c>
       <c r="E94">
-        <v>-27.33041596133803</v>
+        <v>-29.25951871776155</v>
       </c>
       <c r="F94">
-        <v>-5.453202938515499</v>
+        <v>-5.042027747248828</v>
       </c>
       <c r="G94">
-        <v>-0.04147235463878408</v>
+        <v>-1.871783598572263</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.134681610038099</v>
       </c>
       <c r="E95">
-        <v>-29.50196642342121</v>
+        <v>-31.87319768263562</v>
       </c>
       <c r="F95">
-        <v>-5.275835794515858</v>
+        <v>-5.100520341529669</v>
       </c>
       <c r="G95">
-        <v>-1.279808397967486</v>
+        <v>-2.23663882245534</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.711746997276935</v>
       </c>
       <c r="E96">
-        <v>-31.77470110873179</v>
+        <v>-33.03354442728002</v>
       </c>
       <c r="F96">
-        <v>-5.031378908673413</v>
+        <v>-5.058839577394176</v>
       </c>
       <c r="G96">
-        <v>-1.548753807032338</v>
+        <v>-2.449602906451117</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.278374177980276</v>
       </c>
       <c r="E97">
-        <v>-35.03773381122473</v>
+        <v>-34.52338067648552</v>
       </c>
       <c r="F97">
-        <v>-5.810037220558653</v>
+        <v>-5.317802417569088</v>
       </c>
       <c r="G97">
-        <v>-1.152021340151618</v>
+        <v>-2.21061462397113</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.827136920319794</v>
       </c>
       <c r="E98">
-        <v>-36.53627152323596</v>
+        <v>-36.07415433617523</v>
       </c>
       <c r="F98">
-        <v>-5.375032798235323</v>
+        <v>-5.178403039186192</v>
       </c>
       <c r="G98">
-        <v>-1.615259356370757</v>
+        <v>-3.034460434146461</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.328785702615868</v>
       </c>
       <c r="E99">
-        <v>-38.53629244685661</v>
+        <v>-40.86056795908548</v>
       </c>
       <c r="F99">
-        <v>-5.210169012438077</v>
+        <v>-5.412662442639122</v>
       </c>
       <c r="G99">
-        <v>-2.419715301322577</v>
+        <v>-3.488554723586132</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.785116951252212</v>
       </c>
       <c r="E100">
-        <v>-41.31846007989706</v>
+        <v>-42.47678259666004</v>
       </c>
       <c r="F100">
-        <v>-5.525723207942344</v>
+        <v>-5.505681409582458</v>
       </c>
       <c r="G100">
-        <v>-2.726232091712617</v>
+        <v>-4.635844143493798</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-6.159549998367954</v>
       </c>
       <c r="E101">
-        <v>-43.35816628548393</v>
+        <v>-45.42611205498263</v>
       </c>
       <c r="F101">
-        <v>-5.697866497979908</v>
+        <v>-5.201970958766805</v>
       </c>
       <c r="G101">
-        <v>-2.833791716283538</v>
+        <v>-3.668158440182673</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-6.4729968381368</v>
       </c>
       <c r="E102">
-        <v>-46.5060897071759</v>
+        <v>-46.76381421990044</v>
       </c>
       <c r="F102">
-        <v>-5.44959446458717</v>
+        <v>-5.068899277369047</v>
       </c>
       <c r="G102">
-        <v>-3.544880345391292</v>
+        <v>-4.925099749442079</v>
       </c>
     </row>
   </sheetData>
